--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714966</v>
+        <v>113712768</v>
       </c>
       <c r="B2" t="n">
-        <v>90573</v>
+        <v>90149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638543</v>
+        <v>638566</v>
       </c>
       <c r="R2" t="n">
-        <v>7033819</v>
+        <v>7033836</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714960</v>
+        <v>113712788</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>56021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638384</v>
+        <v>638385</v>
       </c>
       <c r="R3" t="n">
-        <v>7033809</v>
+        <v>7033748</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712765</v>
+        <v>113714966</v>
       </c>
       <c r="B4" t="n">
-        <v>90131</v>
+        <v>90573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638565</v>
+        <v>638543</v>
       </c>
       <c r="R4" t="n">
-        <v>7033812</v>
+        <v>7033819</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714959</v>
+        <v>113712764</v>
       </c>
       <c r="B5" t="n">
-        <v>90149</v>
+        <v>90131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638384</v>
+        <v>638518</v>
       </c>
       <c r="R5" t="n">
-        <v>7033822</v>
+        <v>7033808</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714961</v>
+        <v>113714965</v>
       </c>
       <c r="B6" t="n">
         <v>90131</v>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638443</v>
+        <v>638565</v>
       </c>
       <c r="R6" t="n">
-        <v>7033787</v>
+        <v>7033812</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712790</v>
+        <v>113714960</v>
       </c>
       <c r="B7" t="n">
-        <v>90149</v>
+        <v>90131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638332</v>
+        <v>638384</v>
       </c>
       <c r="R7" t="n">
-        <v>7033722</v>
+        <v>7033809</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714962</v>
+        <v>113712759</v>
       </c>
       <c r="B8" t="n">
-        <v>90131</v>
+        <v>90149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638477</v>
+        <v>638384</v>
       </c>
       <c r="R8" t="n">
-        <v>7033795</v>
+        <v>7033822</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714968</v>
+        <v>113712758</v>
       </c>
       <c r="B9" t="n">
-        <v>90149</v>
+        <v>56810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638566</v>
+        <v>638317</v>
       </c>
       <c r="R9" t="n">
-        <v>7033836</v>
+        <v>7033835</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1493,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714964</v>
+        <v>113714961</v>
       </c>
       <c r="B10" t="n">
         <v>90131</v>
@@ -1563,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638518</v>
+        <v>638443</v>
       </c>
       <c r="R10" t="n">
-        <v>7033808</v>
+        <v>7033787</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712788</v>
+        <v>113712790</v>
       </c>
       <c r="B11" t="n">
-        <v>56021</v>
+        <v>90149</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638385</v>
+        <v>638332</v>
       </c>
       <c r="R11" t="n">
-        <v>7033748</v>
+        <v>7033722</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1705,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714958</v>
+        <v>113714962</v>
       </c>
       <c r="B12" t="n">
-        <v>56810</v>
+        <v>90131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638317</v>
+        <v>638477</v>
       </c>
       <c r="R12" t="n">
-        <v>7033835</v>
+        <v>7033795</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712768</v>
+        <v>113712759</v>
       </c>
       <c r="B2" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638566</v>
+        <v>638384</v>
       </c>
       <c r="R2" t="n">
-        <v>7033836</v>
+        <v>7033822</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712788</v>
+        <v>113712762</v>
       </c>
       <c r="B3" t="n">
-        <v>56021</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638385</v>
+        <v>638477</v>
       </c>
       <c r="R3" t="n">
-        <v>7033748</v>
+        <v>7033795</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714966</v>
+        <v>113712789</v>
       </c>
       <c r="B4" t="n">
-        <v>90573</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638543</v>
+        <v>638354</v>
       </c>
       <c r="R4" t="n">
-        <v>7033819</v>
+        <v>7033742</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712764</v>
+        <v>113714966</v>
       </c>
       <c r="B5" t="n">
-        <v>90131</v>
+        <v>90577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638518</v>
+        <v>638543</v>
       </c>
       <c r="R5" t="n">
-        <v>7033808</v>
+        <v>7033819</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714965</v>
+        <v>113714964</v>
       </c>
       <c r="B6" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638565</v>
+        <v>638518</v>
       </c>
       <c r="R6" t="n">
-        <v>7033812</v>
+        <v>7033808</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714960</v>
+        <v>113712768</v>
       </c>
       <c r="B7" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638384</v>
+        <v>638566</v>
       </c>
       <c r="R7" t="n">
-        <v>7033809</v>
+        <v>7033836</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712759</v>
+        <v>113712790</v>
       </c>
       <c r="B8" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638384</v>
+        <v>638332</v>
       </c>
       <c r="R8" t="n">
-        <v>7033822</v>
+        <v>7033722</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714961</v>
+        <v>113714965</v>
       </c>
       <c r="B10" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638443</v>
+        <v>638565</v>
       </c>
       <c r="R10" t="n">
-        <v>7033787</v>
+        <v>7033812</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712790</v>
+        <v>113712761</v>
       </c>
       <c r="B11" t="n">
-        <v>90149</v>
+        <v>90135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638332</v>
+        <v>638443</v>
       </c>
       <c r="R11" t="n">
-        <v>7033722</v>
+        <v>7033787</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714962</v>
+        <v>113712788</v>
       </c>
       <c r="B12" t="n">
-        <v>90131</v>
+        <v>56021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638477</v>
+        <v>638385</v>
       </c>
       <c r="R12" t="n">
-        <v>7033795</v>
+        <v>7033748</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712789</v>
+        <v>113714960</v>
       </c>
       <c r="B13" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638354</v>
+        <v>638384</v>
       </c>
       <c r="R13" t="n">
-        <v>7033742</v>
+        <v>7033809</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712759</v>
+        <v>113712789</v>
       </c>
       <c r="B2" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638384</v>
+        <v>638354</v>
       </c>
       <c r="R2" t="n">
-        <v>7033822</v>
+        <v>7033742</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712762</v>
+        <v>113712764</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638477</v>
+        <v>638518</v>
       </c>
       <c r="R3" t="n">
-        <v>7033795</v>
+        <v>7033808</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712789</v>
+        <v>113712762</v>
       </c>
       <c r="B4" t="n">
         <v>90135</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638354</v>
+        <v>638477</v>
       </c>
       <c r="R4" t="n">
-        <v>7033742</v>
+        <v>7033795</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714966</v>
+        <v>113714965</v>
       </c>
       <c r="B5" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638543</v>
+        <v>638565</v>
       </c>
       <c r="R5" t="n">
-        <v>7033819</v>
+        <v>7033812</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714964</v>
+        <v>113712761</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638518</v>
+        <v>638443</v>
       </c>
       <c r="R6" t="n">
-        <v>7033808</v>
+        <v>7033787</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712768</v>
+        <v>113714959</v>
       </c>
       <c r="B7" t="n">
         <v>90153</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638566</v>
+        <v>638384</v>
       </c>
       <c r="R7" t="n">
-        <v>7033836</v>
+        <v>7033822</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712790</v>
+        <v>113714960</v>
       </c>
       <c r="B8" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638332</v>
+        <v>638384</v>
       </c>
       <c r="R8" t="n">
-        <v>7033722</v>
+        <v>7033809</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714965</v>
+        <v>113714966</v>
       </c>
       <c r="B10" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638565</v>
+        <v>638543</v>
       </c>
       <c r="R10" t="n">
-        <v>7033812</v>
+        <v>7033819</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712761</v>
+        <v>113712788</v>
       </c>
       <c r="B11" t="n">
-        <v>90135</v>
+        <v>56021</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638443</v>
+        <v>638385</v>
       </c>
       <c r="R11" t="n">
-        <v>7033787</v>
+        <v>7033748</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1710,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712788</v>
+        <v>113712790</v>
       </c>
       <c r="B12" t="n">
-        <v>56021</v>
+        <v>90153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638385</v>
+        <v>638332</v>
       </c>
       <c r="R12" t="n">
-        <v>7033748</v>
+        <v>7033722</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714960</v>
+        <v>113714968</v>
       </c>
       <c r="B13" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638384</v>
+        <v>638566</v>
       </c>
       <c r="R13" t="n">
-        <v>7033809</v>
+        <v>7033836</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712789</v>
+        <v>113712762</v>
       </c>
       <c r="B2" t="n">
         <v>90135</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638354</v>
+        <v>638477</v>
       </c>
       <c r="R2" t="n">
-        <v>7033742</v>
+        <v>7033795</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712764</v>
+        <v>113712765</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638518</v>
+        <v>638565</v>
       </c>
       <c r="R3" t="n">
-        <v>7033808</v>
+        <v>7033812</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712762</v>
+        <v>113714958</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638477</v>
+        <v>638317</v>
       </c>
       <c r="R4" t="n">
-        <v>7033795</v>
+        <v>7033835</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714965</v>
+        <v>113714966</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638565</v>
+        <v>638543</v>
       </c>
       <c r="R5" t="n">
-        <v>7033812</v>
+        <v>7033819</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712761</v>
+        <v>113714964</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638443</v>
+        <v>638518</v>
       </c>
       <c r="R6" t="n">
-        <v>7033787</v>
+        <v>7033808</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714959</v>
+        <v>113714961</v>
       </c>
       <c r="B7" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638384</v>
+        <v>638443</v>
       </c>
       <c r="R7" t="n">
-        <v>7033822</v>
+        <v>7033787</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714960</v>
+        <v>113712788</v>
       </c>
       <c r="B8" t="n">
-        <v>90135</v>
+        <v>56021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638384</v>
+        <v>638385</v>
       </c>
       <c r="R8" t="n">
-        <v>7033809</v>
+        <v>7033748</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712758</v>
+        <v>113712760</v>
       </c>
       <c r="B9" t="n">
-        <v>56810</v>
+        <v>90135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638317</v>
+        <v>638384</v>
       </c>
       <c r="R9" t="n">
-        <v>7033835</v>
+        <v>7033809</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1493,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714966</v>
+        <v>113712768</v>
       </c>
       <c r="B10" t="n">
-        <v>90577</v>
+        <v>90153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638543</v>
+        <v>638566</v>
       </c>
       <c r="R10" t="n">
-        <v>7033819</v>
+        <v>7033836</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712788</v>
+        <v>113712759</v>
       </c>
       <c r="B11" t="n">
-        <v>56021</v>
+        <v>90153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638385</v>
+        <v>638384</v>
       </c>
       <c r="R11" t="n">
-        <v>7033748</v>
+        <v>7033822</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1710,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712790</v>
+        <v>113712789</v>
       </c>
       <c r="B12" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638332</v>
+        <v>638354</v>
       </c>
       <c r="R12" t="n">
-        <v>7033722</v>
+        <v>7033742</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714968</v>
+        <v>113712790</v>
       </c>
       <c r="B13" t="n">
         <v>90153</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638566</v>
+        <v>638332</v>
       </c>
       <c r="R13" t="n">
-        <v>7033836</v>
+        <v>7033722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712762</v>
+        <v>113714968</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638477</v>
+        <v>638566</v>
       </c>
       <c r="R2" t="n">
-        <v>7033795</v>
+        <v>7033836</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712765</v>
+        <v>113714965</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714958</v>
+        <v>113714964</v>
       </c>
       <c r="B4" t="n">
-        <v>56810</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638317</v>
+        <v>638518</v>
       </c>
       <c r="R4" t="n">
-        <v>7033835</v>
+        <v>7033808</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714966</v>
+        <v>113712758</v>
       </c>
       <c r="B5" t="n">
-        <v>90577</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638543</v>
+        <v>638317</v>
       </c>
       <c r="R5" t="n">
-        <v>7033819</v>
+        <v>7033835</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714964</v>
+        <v>113712789</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638518</v>
+        <v>638354</v>
       </c>
       <c r="R6" t="n">
-        <v>7033808</v>
+        <v>7033742</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714961</v>
+        <v>113712759</v>
       </c>
       <c r="B7" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638443</v>
+        <v>638384</v>
       </c>
       <c r="R7" t="n">
-        <v>7033787</v>
+        <v>7033822</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712788</v>
+        <v>113714961</v>
       </c>
       <c r="B8" t="n">
-        <v>56021</v>
+        <v>90135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638385</v>
+        <v>638443</v>
       </c>
       <c r="R8" t="n">
-        <v>7033748</v>
+        <v>7033787</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712760</v>
+        <v>113712766</v>
       </c>
       <c r="B9" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638384</v>
+        <v>638543</v>
       </c>
       <c r="R9" t="n">
-        <v>7033809</v>
+        <v>7033819</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712768</v>
+        <v>113712788</v>
       </c>
       <c r="B10" t="n">
-        <v>90153</v>
+        <v>56021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638566</v>
+        <v>638385</v>
       </c>
       <c r="R10" t="n">
-        <v>7033836</v>
+        <v>7033748</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1609,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712759</v>
+        <v>113712762</v>
       </c>
       <c r="B11" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638384</v>
+        <v>638477</v>
       </c>
       <c r="R11" t="n">
-        <v>7033822</v>
+        <v>7033795</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712789</v>
+        <v>113712760</v>
       </c>
       <c r="B12" t="n">
         <v>90135</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638354</v>
+        <v>638384</v>
       </c>
       <c r="R12" t="n">
-        <v>7033742</v>
+        <v>7033809</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714968</v>
+        <v>113714966</v>
       </c>
       <c r="B2" t="n">
-        <v>90153</v>
+        <v>90577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638566</v>
+        <v>638543</v>
       </c>
       <c r="R2" t="n">
-        <v>7033836</v>
+        <v>7033819</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714965</v>
+        <v>113714958</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>56810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638565</v>
+        <v>638317</v>
       </c>
       <c r="R3" t="n">
-        <v>7033812</v>
+        <v>7033835</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113714964</v>
+        <v>113712759</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638518</v>
+        <v>638384</v>
       </c>
       <c r="R4" t="n">
-        <v>7033808</v>
+        <v>7033822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712758</v>
+        <v>113712761</v>
       </c>
       <c r="B5" t="n">
-        <v>56810</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638317</v>
+        <v>638443</v>
       </c>
       <c r="R5" t="n">
-        <v>7033835</v>
+        <v>7033787</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla hackringar i död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712789</v>
+        <v>113712760</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638354</v>
+        <v>638384</v>
       </c>
       <c r="R6" t="n">
-        <v>7033742</v>
+        <v>7033809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712759</v>
+        <v>113712788</v>
       </c>
       <c r="B7" t="n">
-        <v>90153</v>
+        <v>56021</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638384</v>
+        <v>638385</v>
       </c>
       <c r="R7" t="n">
-        <v>7033822</v>
+        <v>7033748</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714961</v>
+        <v>113712768</v>
       </c>
       <c r="B8" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638443</v>
+        <v>638566</v>
       </c>
       <c r="R8" t="n">
-        <v>7033787</v>
+        <v>7033836</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712766</v>
+        <v>113714965</v>
       </c>
       <c r="B9" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638543</v>
+        <v>638565</v>
       </c>
       <c r="R9" t="n">
-        <v>7033819</v>
+        <v>7033812</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712788</v>
+        <v>113712789</v>
       </c>
       <c r="B10" t="n">
-        <v>56021</v>
+        <v>90135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638385</v>
+        <v>638354</v>
       </c>
       <c r="R10" t="n">
-        <v>7033748</v>
+        <v>7033742</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,11 +1609,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tre stycken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712760</v>
+        <v>113714964</v>
       </c>
       <c r="B12" t="n">
         <v>90135</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638384</v>
+        <v>638518</v>
       </c>
       <c r="R12" t="n">
-        <v>7033809</v>
+        <v>7033808</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 29916-2020 artfynd.xlsx
+++ b/artfynd/A 29916-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
